--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488027_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488027_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.14</v>
+        <v>5.4103</v>
       </c>
       <c r="E2" t="n">
-        <v>2.7554</v>
+        <v>2.8573</v>
       </c>
       <c r="F2" t="n">
-        <v>2.3845</v>
+        <v>2.553</v>
       </c>
       <c r="G2" t="n">
         <v>2.104</v>
@@ -610,13 +610,13 @@
         <v>1.9822</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.42</v>
+        <v>-0.1496</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.5064</v>
+        <v>-0.4045</v>
       </c>
       <c r="U2" t="n">
-        <v>0.08649999999999999</v>
+        <v>0.2549</v>
       </c>
       <c r="V2" t="n">
         <v>1.4737</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.858</v>
+        <v>3.5806</v>
       </c>
       <c r="E3" t="n">
-        <v>0.2069</v>
+        <v>0.6768</v>
       </c>
       <c r="F3" t="n">
-        <v>2.651</v>
+        <v>2.9037</v>
       </c>
       <c r="G3" t="n">
         <v>1.2902</v>
@@ -688,13 +688,13 @@
         <v>2.5769</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1677</v>
+        <v>-0.4451</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.0608</v>
+        <v>-0.5909</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.107</v>
+        <v>0.1457</v>
       </c>
       <c r="V3" t="n">
         <v>1.3479</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.704</v>
+        <v>0.4814</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.6665</v>
+        <v>-1.4398</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3706</v>
+        <v>1.9213</v>
       </c>
       <c r="G4" t="n">
         <v>-1.8628</v>
@@ -766,13 +766,13 @@
         <v>3.3698</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2914</v>
+        <v>0.0688</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.068</v>
+        <v>-0.8413</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3594</v>
+        <v>0.9101</v>
       </c>
       <c r="V4" t="n">
         <v>2.0772</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0982</v>
+        <v>0.3186</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.1183</v>
+        <v>-0.9540999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>1.2165</v>
+        <v>1.2726</v>
       </c>
       <c r="G5" t="n">
         <v>-0.4202</v>
@@ -844,13 +844,13 @@
         <v>0.9911</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4728</v>
+        <v>-0.2523</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7488</v>
+        <v>-0.5845</v>
       </c>
       <c r="U5" t="n">
-        <v>0.276</v>
+        <v>0.3322</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2745</v>
+        <v>-1.1612</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5152</v>
+        <v>-2.2054</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2407</v>
+        <v>1.0442</v>
       </c>
       <c r="G6" t="n">
         <v>0.6177</v>
@@ -922,13 +922,13 @@
         <v>3.7662</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9335</v>
+        <v>0.0468</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2279</v>
+        <v>-0.4623</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7056</v>
+        <v>0.5091</v>
       </c>
       <c r="V6" t="n">
         <v>1.5441</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3885</v>
+        <v>-1.3324</v>
       </c>
       <c r="E7" t="n">
         <v>-0.5316</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.8569</v>
+        <v>-0.8008</v>
       </c>
       <c r="G7" t="n">
         <v>-1.1029</v>
@@ -1000,13 +1000,13 @@
         <v>1.3876</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.4838</v>
+        <v>-0.4276</v>
       </c>
       <c r="T7" t="n">
         <v>-0.312</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1718</v>
+        <v>-0.1157</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.4495</v>
+        <v>-1.5951</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.1799</v>
+        <v>-3.157</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7304</v>
+        <v>1.5619</v>
       </c>
       <c r="G8" t="n">
         <v>-2.4752</v>
@@ -1078,13 +1078,13 @@
         <v>1.784</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2328</v>
+        <v>0.0872</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.756</v>
+        <v>-0.7331</v>
       </c>
       <c r="U8" t="n">
-        <v>0.9888</v>
+        <v>0.8203</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1754</v>
+        <v>-2.1088</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5176</v>
+        <v>-2.6195</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3422</v>
+        <v>0.5107</v>
       </c>
       <c r="G9" t="n">
         <v>-3.6319</v>
@@ -1156,13 +1156,13 @@
         <v>1.5858</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.1997</v>
+        <v>-0.1331</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0696</v>
+        <v>-0.1715</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.13</v>
+        <v>0.0384</v>
       </c>
       <c r="V9" t="n">
         <v>0.0704</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.7107</v>
+        <v>-5.168</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.9113</v>
+        <v>-4.4809</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7995</v>
+        <v>-0.6872</v>
       </c>
       <c r="G10" t="n">
         <v>-5.6204</v>
@@ -1234,13 +1234,13 @@
         <v>2.3787</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.6871</v>
+        <v>-1.1444</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.5599</v>
+        <v>-1.1295</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1271</v>
+        <v>-0.0148</v>
       </c>
       <c r="V10" t="n">
         <v>0.4074</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.198400000000001</v>
+        <v>-1.574599999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.4781</v>
+        <v>-11.8542</v>
       </c>
       <c r="F11" t="n">
-        <v>10.2795</v>
+        <v>10.2794</v>
       </c>
       <c r="G11" t="n">
         <v>-11.1015</v>
@@ -1312,13 +1312,13 @@
         <v>19.8223</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.9734</v>
+        <v>-2.3493</v>
       </c>
       <c r="T11" t="n">
-        <v>-5.8536</v>
+        <v>-5.2296</v>
       </c>
       <c r="U11" t="n">
-        <v>2.8804</v>
+        <v>2.8802</v>
       </c>
       <c r="V11" t="n">
         <v>6.920699999999999</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>4.6127</v>
+        <v>4.3456</v>
       </c>
       <c r="E12" t="n">
-        <v>2.466</v>
+        <v>2.0586</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1467</v>
+        <v>2.2871</v>
       </c>
       <c r="G12" t="n">
         <v>3.7627</v>
@@ -1390,13 +1390,13 @@
         <v>2.3787</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5745</v>
+        <v>0.3074</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0769</v>
+        <v>-0.4844</v>
       </c>
       <c r="U12" t="n">
-        <v>0.6514</v>
+        <v>0.7917999999999999</v>
       </c>
       <c r="V12" t="n">
         <v>0.8701</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.612</v>
+        <v>3.7805</v>
       </c>
       <c r="E13" t="n">
         <v>2.4271</v>
       </c>
       <c r="F13" t="n">
-        <v>1.1849</v>
+        <v>1.3534</v>
       </c>
       <c r="G13" t="n">
         <v>3.6356</v>
@@ -1468,13 +1468,13 @@
         <v>1.784</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1747</v>
+        <v>0.3432</v>
       </c>
       <c r="T13" t="n">
         <v>-0.3192</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4939</v>
+        <v>0.6624</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MAYOR MARTIN</t>
+          <t>E. LOPEZ GARCIA</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1686</v>
+        <v>3.2855</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4283</v>
+        <v>0.5148</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7403</v>
+        <v>2.7708</v>
       </c>
       <c r="G14" t="n">
-        <v>4.2593</v>
+        <v>2.049</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7338</v>
+        <v>-1.4597</v>
       </c>
       <c r="I14" t="n">
-        <v>2.5255</v>
+        <v>3.5087</v>
       </c>
       <c r="J14" t="n">
-        <v>5.2824</v>
+        <v>2.6176</v>
       </c>
       <c r="K14" t="n">
-        <v>2.2535</v>
+        <v>-0.1949</v>
       </c>
       <c r="L14" t="n">
-        <v>3.0289</v>
+        <v>2.8124</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.0232</v>
+        <v>-0.5686</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.5198</v>
+        <v>-1.2648</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.5034</v>
+        <v>0.6962</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.784</v>
+        <v>0.3964</v>
       </c>
       <c r="Q14" t="n">
-        <v>-3.9645</v>
+        <v>-1.9822</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1805</v>
+        <v>2.3787</v>
       </c>
       <c r="S14" t="n">
-        <v>1.2969</v>
+        <v>0.5736</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1103</v>
+        <v>-0.3871</v>
       </c>
       <c r="U14" t="n">
-        <v>1.1865</v>
+        <v>0.9607</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.6036</v>
+        <v>0.2666</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2666</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.6036</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>E. LOPEZ GARCIA</t>
+          <t>A. MAYOR MARTIN</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5339</v>
+        <v>2.5645</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.0964</v>
+        <v>1.0208</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6304</v>
+        <v>1.5437</v>
       </c>
       <c r="G15" t="n">
-        <v>2.049</v>
+        <v>4.2593</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.4597</v>
+        <v>1.7338</v>
       </c>
       <c r="I15" t="n">
-        <v>3.5087</v>
+        <v>2.5255</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6176</v>
+        <v>5.2824</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.1949</v>
+        <v>2.2535</v>
       </c>
       <c r="L15" t="n">
-        <v>2.8124</v>
+        <v>3.0289</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.5686</v>
+        <v>-1.0232</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2648</v>
+        <v>-0.5198</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6962</v>
+        <v>-0.5034</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3964</v>
+        <v>-1.784</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.9822</v>
+        <v>-3.9645</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3787</v>
+        <v>2.1805</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.1781</v>
+        <v>0.6928</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9984</v>
+        <v>-0.2972</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8203</v>
+        <v>0.99</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2666</v>
+        <v>-0.6036</v>
       </c>
       <c r="W15" t="n">
-        <v>0.2666</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. TERRON FERNANDEZ</t>
+          <t>J. RAMIREZ GUERRA-LIBRERO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.1773</v>
+        <v>-1.0226</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.3461</v>
+        <v>-2.2376</v>
       </c>
       <c r="F16" t="n">
-        <v>1.1688</v>
+        <v>1.215</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8539</v>
+        <v>1.7052</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9246</v>
+        <v>1.0222</v>
       </c>
       <c r="I16" t="n">
-        <v>0.0708</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.9661999999999999</v>
+        <v>0.9522</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.335</v>
+        <v>0.9484</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6312</v>
+        <v>0.0039</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1123</v>
+        <v>0.7529</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5896</v>
+        <v>0.0738</v>
       </c>
       <c r="O16" t="n">
-        <v>0.7019</v>
+        <v>0.6791</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5947</v>
+        <v>-2.3787</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9822</v>
+        <v>-2.9733</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3876</v>
+        <v>0.5947</v>
       </c>
       <c r="S16" t="n">
-        <v>1.9452</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4062</v>
+        <v>-0.2165</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5391</v>
+        <v>0.1339</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.674</v>
+        <v>-0.2666</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1962</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.8701</v>
+        <v>-0.2666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. RAMIREZ GUERRA-LIBRERO</t>
+          <t>D. TERRON FERNANDEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4863</v>
+        <v>-1.7334</v>
       </c>
       <c r="E17" t="n">
-        <v>-2.6451</v>
+        <v>-2.8741</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1588</v>
+        <v>1.1407</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7052</v>
+        <v>-0.8539</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0222</v>
+        <v>-0.9246</v>
       </c>
       <c r="I17" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.0708</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9522</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9484</v>
+        <v>-0.335</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0039</v>
+        <v>-0.6312</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7529</v>
+        <v>0.1123</v>
       </c>
       <c r="N17" t="n">
-        <v>0.0738</v>
+        <v>-0.5896</v>
       </c>
       <c r="O17" t="n">
-        <v>0.6791</v>
+        <v>0.7019</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.3787</v>
+        <v>-0.5947</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.9733</v>
+        <v>-1.9822</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5947</v>
+        <v>1.3876</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5462</v>
+        <v>0.3891</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.624</v>
+        <v>-0.1219</v>
       </c>
       <c r="U17" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.511</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.2666</v>
+        <v>-0.674</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.1962</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2666</v>
+        <v>-0.8701</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.6296</v>
+        <v>-2.1836</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.3044</v>
+        <v>-2.9988</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6748</v>
+        <v>0.8152</v>
       </c>
       <c r="G18" t="n">
         <v>-1.7988</v>
@@ -1858,13 +1858,13 @@
         <v>0.9911</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6148</v>
+        <v>-0.1688</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7488</v>
+        <v>-0.4432</v>
       </c>
       <c r="U18" t="n">
-        <v>0.1339</v>
+        <v>0.2743</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2071</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.2129</v>
+        <v>-3.318</v>
       </c>
       <c r="E19" t="n">
-        <v>-3.824</v>
+        <v>-3.6203</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6112</v>
+        <v>0.3023</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0046</v>
@@ -1936,13 +1936,13 @@
         <v>1.784</v>
       </c>
       <c r="S19" t="n">
-        <v>1.1486</v>
+        <v>1.0434</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0696</v>
+        <v>0.1341</v>
       </c>
       <c r="U19" t="n">
-        <v>1.2182</v>
+        <v>0.9093</v>
       </c>
       <c r="V19" t="n">
         <v>-3.1586</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.2228</v>
+        <v>-3.5201</v>
       </c>
       <c r="E20" t="n">
-        <v>-5.385</v>
+        <v>-4.57</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1622</v>
+        <v>1.0499</v>
       </c>
       <c r="G20" t="n">
         <v>-0.653</v>
@@ -2014,13 +2014,13 @@
         <v>1.3876</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8274</v>
+        <v>-0.1248</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.5599</v>
+        <v>-0.745</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7325</v>
+        <v>0.6202</v>
       </c>
       <c r="V20" t="n">
         <v>-2.1476</v>
@@ -2047,10 +2047,10 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>2.198300000000001</v>
+        <v>2.198400000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>-10.2796</v>
+        <v>-10.2795</v>
       </c>
       <c r="F21" t="n">
         <v>12.4781</v>
@@ -2092,13 +2092,13 @@
         <v>14.8669</v>
       </c>
       <c r="S21" t="n">
-        <v>2.9734</v>
+        <v>2.9733</v>
       </c>
       <c r="T21" t="n">
-        <v>-2.8803</v>
+        <v>-2.8804</v>
       </c>
       <c r="U21" t="n">
-        <v>5.8536</v>
+        <v>5.853599999999999</v>
       </c>
       <c r="V21" t="n">
         <v>-6.9208</v>
